--- a/exports/INDIGO_full_report.xlsx
+++ b/exports/INDIGO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>8.83</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44585.38541666666</v>
+        <v>44585.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>2040.4</v>
+        <v>1991</v>
       </c>
       <c r="I2" t="n">
         <v>2039.309957472075</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.09</v>
+        <v>-3.48</v>
       </c>
       <c r="L2" t="n">
-        <v>4.16</v>
+        <v>4.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.39</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>8.16</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44596.55208333334</v>
+        <v>44599.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1971</v>
+        <v>2154.1</v>
       </c>
       <c r="I3" t="n">
         <v>2013.622105003715</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>-8.19</v>
       </c>
       <c r="L3" t="n">
-        <v>2.61</v>
+        <v>9.59</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7</v>
+        <v>1.73</v>
       </c>
       <c r="N3" t="n">
-        <v>5.44</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="O3" t="n">
         <v>-4.69</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.87</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44610.55208333334</v>
+        <v>44613.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2113</v>
+        <v>2076.4</v>
       </c>
       <c r="I4" t="n">
         <v>2088.546362175078</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.91</v>
+        <v>-3.61</v>
       </c>
       <c r="L4" t="n">
         <v>7.41</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>8.84</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1715</v>
+        <v>1806.95</v>
       </c>
       <c r="I5" t="n">
         <v>1780.064162906042</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>17.41</v>
+        <v>12.98</v>
       </c>
       <c r="L5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>4.39</v>
+        <v>4.96</v>
       </c>
       <c r="N5" t="n">
         <v>7.18</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.31</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44663.55208333334</v>
+        <v>44664.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1931.3</v>
+        <v>1908.5</v>
       </c>
       <c r="I6" t="n">
         <v>1911.672499237273</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>6.88</v>
+        <v>5.62</v>
       </c>
       <c r="L6" t="n">
         <v>2.92</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.77</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44707.38541666666</v>
+        <v>44707.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>1767</v>
+        <v>1813.75</v>
       </c>
       <c r="I7" t="n">
         <v>1773.762749178029</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>7.41</v>
+        <v>4.96</v>
       </c>
       <c r="L7" t="n">
         <v>2.2</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.86</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>1735</v>
+        <v>1647.75</v>
       </c>
       <c r="I8" t="n">
         <v>1710.599701596424</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.34</v>
+        <v>-9.15</v>
       </c>
       <c r="L8" t="n">
-        <v>5.02</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>1.33</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>5.13</v>
       </c>
       <c r="O8" t="n">
         <v>10.06</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.25</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1675.1</v>
+        <v>1696.05</v>
       </c>
       <c r="I9" t="n">
         <v>1695.174589367706</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.66</v>
+        <v>-2.93</v>
       </c>
       <c r="L9" t="n">
         <v>5.96</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44802.38541666666</v>
+        <v>44802.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>1957</v>
+        <v>1955.5</v>
       </c>
       <c r="I10" t="n">
         <v>1955.807073091288</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>15.39</v>
+        <v>15.3</v>
       </c>
       <c r="L10" t="n">
         <v>2.76</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.89</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44866.38541666666</v>
+        <v>44866.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>1812.55</v>
+        <v>1820</v>
       </c>
       <c r="I11" t="n">
         <v>1817.283100532433</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>63.83333333333334</v>
+        <v>64</v>
       </c>
       <c r="K11" t="n">
-        <v>7.31</v>
+        <v>6.93</v>
       </c>
       <c r="L11" t="n">
         <v>5.73</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>4.06</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44872.55208333334</v>
+        <v>44874.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1776</v>
+        <v>1689.6</v>
       </c>
       <c r="I12" t="n">
         <v>1746.180439944943</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.42</v>
+        <v>-7.16</v>
       </c>
       <c r="L12" t="n">
-        <v>2.86</v>
+        <v>7.91</v>
       </c>
       <c r="M12" t="n">
         <v>1.62</v>
       </c>
       <c r="N12" t="n">
-        <v>1.18</v>
+        <v>3.14</v>
       </c>
       <c r="O12" t="n">
         <v>2.12</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.51</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44886.55208333334</v>
+        <v>44887.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1789.25</v>
+        <v>1825.2</v>
       </c>
       <c r="I13" t="n">
         <v>1804.095691810107</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.9</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>7.3</v>
+        <v>8.27</v>
       </c>
       <c r="M13" t="n">
         <v>0.83</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.79</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1970.85</v>
+        <v>1916.9</v>
       </c>
       <c r="I14" t="n">
         <v>1958.258066104664</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K14" t="n">
-        <v>7.98</v>
+        <v>5.02</v>
       </c>
       <c r="L14" t="n">
         <v>1.99</v>
@@ -1239,7 +1406,7 @@
         <v>1.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.61</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.41</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44928.38541666666</v>
+        <v>44928.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>2031.7</v>
+        <v>2039.35</v>
       </c>
       <c r="I15" t="n">
         <v>2035.935817116271</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.99</v>
+        <v>-6.39</v>
       </c>
       <c r="L15" t="n">
         <v>7.1</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.05</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44963.55208333334</v>
+        <v>44964.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2065</v>
+        <v>2038.55</v>
       </c>
       <c r="I16" t="n">
         <v>2040.012298998897</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>1.26</v>
+        <v>-0.04</v>
       </c>
       <c r="L16" t="n">
         <v>2.4</v>
@@ -1353,7 +1544,7 @@
         <v>0.51</v>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
         <v>1.91</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45016.38541666666</v>
+        <v>45016.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>1907.5</v>
+        <v>1915</v>
       </c>
       <c r="I17" t="n">
         <v>1907.970918045287</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>6.43</v>
+        <v>6.06</v>
       </c>
       <c r="L17" t="n">
         <v>3.06</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.28</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45089.55208333334</v>
+        <v>45090.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2415.3</v>
+        <v>2338.3</v>
       </c>
       <c r="I18" t="n">
         <v>2370.428310570323</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>73</v>
+        <v>73.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>26.13</v>
+        <v>22.1</v>
       </c>
       <c r="L18" t="n">
         <v>2.82</v>
@@ -1467,7 +1682,7 @@
         <v>0.8</v>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>3.17</v>
       </c>
       <c r="O18" t="n">
         <v>4.36</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45097.55208333334</v>
+        <v>45098.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2439</v>
+        <v>2465.15</v>
       </c>
       <c r="I19" t="n">
         <v>2460.024357934812</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.31</v>
+        <v>-5.42</v>
       </c>
       <c r="L19" t="n">
         <v>6.49</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.68</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45131.55208333334</v>
+        <v>45132.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2666.35</v>
+        <v>2577.1</v>
       </c>
       <c r="I20" t="n">
         <v>2618.444052383048</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>8.16</v>
+        <v>4.54</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -1581,7 +1820,7 @@
         <v>0.73</v>
       </c>
       <c r="N20" t="n">
-        <v>2.09</v>
+        <v>3.06</v>
       </c>
       <c r="O20" t="n">
         <v>1.35</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>6.71</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45203.55208333334</v>
+        <v>45204.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2395</v>
+        <v>2449.8</v>
       </c>
       <c r="I21" t="n">
         <v>2436.456835261885</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>72</v>
       </c>
       <c r="K21" t="n">
-        <v>7.07</v>
+        <v>4.94</v>
       </c>
       <c r="L21" t="n">
         <v>3.84</v>
       </c>
       <c r="M21" t="n">
-        <v>0.97</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>2.13</v>
+        <v>3.38</v>
       </c>
       <c r="O21" t="n">
         <v>-3.06</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.86</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2530</v>
+        <v>2437.75</v>
       </c>
       <c r="I22" t="n">
         <v>2499.763923867764</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>3.27</v>
+        <v>-0.49</v>
       </c>
       <c r="L22" t="n">
         <v>2.02</v>
@@ -1695,7 +1958,7 @@
         <v>1.26</v>
       </c>
       <c r="N22" t="n">
-        <v>2.27</v>
+        <v>3.48</v>
       </c>
       <c r="O22" t="n">
         <v>3.38</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>6.41</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2505.15</v>
+        <v>2548</v>
       </c>
       <c r="I23" t="n">
         <v>2527.929989787991</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.76</v>
+        <v>-4.52</v>
       </c>
       <c r="L23" t="n">
-        <v>4.19</v>
+        <v>5.84</v>
       </c>
       <c r="M23" t="n">
         <v>1.18</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>5.89</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3041.6</v>
+        <v>2953.25</v>
       </c>
       <c r="I24" t="n">
         <v>2973.032201713162</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>75.16666666666667</v>
+        <v>78</v>
       </c>
       <c r="K24" t="n">
-        <v>19.37</v>
+        <v>15.9</v>
       </c>
       <c r="L24" t="n">
         <v>2.42</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>7.19</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45323.38541666666</v>
+        <v>45323.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>3015</v>
+        <v>3068</v>
       </c>
       <c r="I25" t="n">
         <v>3015.930573351224</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.09</v>
+        <v>-3.89</v>
       </c>
       <c r="L25" t="n">
-        <v>3.89</v>
+        <v>4.36</v>
       </c>
       <c r="M25" t="n">
         <v>0.87</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.22</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45336.55208333334</v>
+        <v>45337.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3097</v>
+        <v>3029.85</v>
       </c>
       <c r="I26" t="n">
         <v>3036.708831576331</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>0.95</v>
+        <v>-1.24</v>
       </c>
       <c r="L26" t="n">
         <v>2.73</v>
@@ -1923,7 +2234,7 @@
         <v>0.33</v>
       </c>
       <c r="N26" t="n">
-        <v>1.29</v>
+        <v>2.06</v>
       </c>
       <c r="O26" t="n">
         <v>3.47</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.16</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45358.55208333334</v>
+        <v>45362.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3100</v>
+        <v>3216.1</v>
       </c>
       <c r="I27" t="n">
         <v>3212.866961413101</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.32</v>
+        <v>-6.15</v>
       </c>
       <c r="L27" t="n">
-        <v>6.12</v>
+        <v>6.18</v>
       </c>
       <c r="M27" t="n">
         <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>1.66</v>
+        <v>3.71</v>
       </c>
       <c r="O27" t="n">
         <v>-2.06</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>3605.95</v>
+        <v>3533.1</v>
       </c>
       <c r="I28" t="n">
         <v>3605.721095226277</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n">
-        <v>12.12</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>6.1</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.95</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45406.55208333334</v>
+        <v>45407.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>3758.35</v>
+        <v>3783</v>
       </c>
       <c r="I29" t="n">
         <v>3772.824738277521</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.38</v>
+        <v>-7.07</v>
       </c>
       <c r="L29" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="M29" t="n">
         <v>1.96</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.33</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45440.55208333334</v>
+        <v>45441.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>4190</v>
+        <v>4066.25</v>
       </c>
       <c r="I30" t="n">
         <v>4163.874476721113</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K30" t="n">
-        <v>10.76</v>
+        <v>7.49</v>
       </c>
       <c r="L30" t="n">
         <v>1.48</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>7.75</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>4200</v>
+        <v>4299.25</v>
       </c>
       <c r="I31" t="n">
         <v>4298.770698323912</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.29</v>
+        <v>-5.73</v>
       </c>
       <c r="L31" t="n">
-        <v>3.73</v>
+        <v>6.34</v>
       </c>
       <c r="M31" t="n">
-        <v>0.67</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
         <v>2.71</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.01</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45462.38541666666</v>
+        <v>45462.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>4238.2</v>
+        <v>4225.15</v>
       </c>
       <c r="I32" t="n">
         <v>4227.329481007184</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.42</v>
+        <v>-1.72</v>
       </c>
       <c r="L32" t="n">
         <v>10.03</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>5.6</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45485.55208333334</v>
+        <v>45488.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>4336.1</v>
+        <v>4395.8</v>
       </c>
       <c r="I33" t="n">
         <v>4389.388701498353</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.63</v>
+        <v>-4.04</v>
       </c>
       <c r="L33" t="n">
-        <v>3.4</v>
+        <v>4.73</v>
       </c>
       <c r="M33" t="n">
         <v>0.98</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>4.62</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>4312.55</v>
+        <v>4212.05</v>
       </c>
       <c r="I34" t="n">
         <v>4270.993600862636</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.89</v>
+        <v>-4.18</v>
       </c>
       <c r="L34" t="n">
-        <v>5.11</v>
+        <v>5.3</v>
       </c>
       <c r="M34" t="n">
         <v>1.36</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>6.39</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45525.55208333334</v>
+        <v>45526.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>4308.65</v>
+        <v>4439.35</v>
       </c>
       <c r="I35" t="n">
         <v>4395.811678146544</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.29</v>
+        <v>-5.4</v>
       </c>
       <c r="L35" t="n">
-        <v>3.32</v>
+        <v>6.17</v>
       </c>
       <c r="M35" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="N35" t="n">
-        <v>1.84</v>
+        <v>4.11</v>
       </c>
       <c r="O35" t="n">
         <v>-1.96</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.09</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45559.55208333334</v>
+        <v>45560.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>4815.3</v>
+        <v>4768.2</v>
       </c>
       <c r="I36" t="n">
         <v>4784.410836159609</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K36" t="n">
-        <v>8.470000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="L36" t="n">
         <v>1.43</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>4.86</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45614.55208333334</v>
+        <v>45615.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>3973</v>
+        <v>4097.95</v>
       </c>
       <c r="I37" t="n">
         <v>4077.75189086543</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K37" t="n">
-        <v>16.68</v>
+        <v>14.06</v>
       </c>
       <c r="L37" t="n">
         <v>4.02</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.14</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45660.55208333334</v>
+        <v>45663.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>4462.3</v>
+        <v>4288.5</v>
       </c>
       <c r="I38" t="n">
         <v>4452.013733837939</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K38" t="n">
-        <v>8.890000000000001</v>
+        <v>4.65</v>
       </c>
       <c r="L38" t="n">
         <v>2.83</v>
@@ -2607,7 +3062,7 @@
         <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>1.78</v>
+        <v>4.49</v>
       </c>
       <c r="O38" t="n">
         <v>1.69</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.01</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45684.55208333334</v>
+        <v>45685.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>4193</v>
+        <v>4262.95</v>
       </c>
       <c r="I39" t="n">
         <v>4228.811875685196</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>2.23</v>
+        <v>0.6</v>
       </c>
       <c r="L39" t="n">
         <v>4.56</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.45</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45777.38541666666</v>
+        <v>45777.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>5248.5</v>
+        <v>5234</v>
       </c>
       <c r="I40" t="n">
         <v>5238.725122223537</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>92</v>
+        <v>92.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>23.12</v>
+        <v>22.78</v>
       </c>
       <c r="L40" t="n">
         <v>2.47</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>6.15</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>5114.5</v>
+        <v>5462</v>
       </c>
       <c r="I41" t="n">
         <v>5415.881866353329</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>2.28</v>
+        <v>-4.36</v>
       </c>
       <c r="L41" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="M41" t="n">
-        <v>1.46</v>
+        <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>3.61</v>
+        <v>7.32</v>
       </c>
       <c r="O41" t="n">
         <v>-0.55</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>8.41</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>5444</v>
+        <v>5235.5</v>
       </c>
       <c r="I42" t="n">
         <v>5440.494134808107</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.33</v>
+        <v>-4.15</v>
       </c>
       <c r="L42" t="n">
-        <v>4.24</v>
+        <v>5.24</v>
       </c>
       <c r="M42" t="n">
-        <v>2.84</v>
+        <v>4.48</v>
       </c>
       <c r="N42" t="n">
         <v>3.25</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>5.96</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>5460</v>
+        <v>5647</v>
       </c>
       <c r="I43" t="n">
         <v>5494.685911204861</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.29</v>
+        <v>-7.86</v>
       </c>
       <c r="L43" t="n">
-        <v>4.76</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3</v>
+        <v>3.14</v>
       </c>
       <c r="N43" t="n">
         <v>2.86</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>5.35</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45866.38541666666</v>
+        <v>45866.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>5784</v>
+        <v>5754</v>
       </c>
       <c r="I44" t="n">
         <v>5772.893093410388</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>2.43</v>
+        <v>1.89</v>
       </c>
       <c r="L44" t="n">
         <v>1.49</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>3.92</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45880.55208333334</v>
+        <v>45881.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>5877.5</v>
+        <v>5944</v>
       </c>
       <c r="I45" t="n">
         <v>5938.032179804645</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.15</v>
+        <v>-3.3</v>
       </c>
       <c r="L45" t="n">
-        <v>3.07</v>
+        <v>3.62</v>
       </c>
       <c r="M45" t="n">
         <v>0.61</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>5.39</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>6031</v>
+        <v>5758.5</v>
       </c>
       <c r="I46" t="n">
         <v>5877.302851428834</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>1.46</v>
+        <v>-3.12</v>
       </c>
       <c r="L46" t="n">
-        <v>2.02</v>
+        <v>3.92</v>
       </c>
       <c r="M46" t="n">
-        <v>0.98</v>
+        <v>2.59</v>
       </c>
       <c r="N46" t="n">
-        <v>1.42</v>
+        <v>4.92</v>
       </c>
       <c r="O46" t="n">
         <v>0.76</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.07</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45940.55208333334</v>
+        <v>45943.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>5736</v>
+        <v>5795</v>
       </c>
       <c r="I47" t="n">
         <v>5754.270787411469</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K47" t="n">
-        <v>0.39</v>
+        <v>-0.63</v>
       </c>
       <c r="L47" t="n">
         <v>2.02</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>3.99</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45953.55208333334</v>
+        <v>45954.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>5791.5</v>
+        <v>5713</v>
       </c>
       <c r="I48" t="n">
         <v>5756.130316403925</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.06</v>
+        <v>-1.42</v>
       </c>
       <c r="L48" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="M48" t="n">
         <v>0.07000000000000001</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>4.32</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45973.55208333334</v>
+        <v>45974.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>5790</v>
+        <v>5932</v>
       </c>
       <c r="I49" t="n">
         <v>5840.919955762545</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.35</v>
+        <v>-3.83</v>
       </c>
       <c r="L49" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="M49" t="n">
         <v>2.13</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.39</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45992.55208333334</v>
+        <v>45993.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>5772.5</v>
+        <v>5683</v>
       </c>
       <c r="I50" t="n">
         <v>5704.874120667182</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.69</v>
+        <v>-4.2</v>
       </c>
       <c r="L50" t="n">
         <v>4.35</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>4.94</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>4734.5</v>
+        <v>4927</v>
       </c>
       <c r="I51" t="n">
         <v>4903.526997420706</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K51" t="n">
-        <v>16.69</v>
+        <v>13.3</v>
       </c>
       <c r="L51" t="n">
         <v>2.16</v>
@@ -3348,7 +3959,7 @@
         <v>0.78</v>
       </c>
       <c r="N51" t="n">
-        <v>2.99</v>
+        <v>4.28</v>
       </c>
       <c r="O51" t="n">
         <v>-1.26</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.78</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46044.55208333334</v>
+        <v>46045.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>4929</v>
+        <v>4705</v>
       </c>
       <c r="I52" t="n">
         <v>4744.650632089228</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>0.04</v>
+        <v>-4.51</v>
       </c>
       <c r="L52" t="n">
-        <v>3.59</v>
+        <v>4.88</v>
       </c>
       <c r="M52" t="n">
-        <v>0.35</v>
+        <v>1.03</v>
       </c>
       <c r="N52" t="n">
-        <v>2.74</v>
+        <v>4.34</v>
       </c>
       <c r="O52" t="n">
         <v>4.28</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.57</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>4690</v>
+        <v>4905.5</v>
       </c>
       <c r="I53" t="n">
         <v>4822.015129700322</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>0.32</v>
+        <v>-4.26</v>
       </c>
       <c r="L53" t="n">
-        <v>3.68</v>
+        <v>6.44</v>
       </c>
       <c r="M53" t="n">
-        <v>0.63</v>
+        <v>5.54</v>
       </c>
       <c r="N53" t="n">
-        <v>2.18</v>
+        <v>5.5</v>
       </c>
       <c r="O53" t="n">
         <v>-4.34</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>6.03</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>4830.3</v>
+        <v>4543.5</v>
       </c>
       <c r="I54" t="n">
         <v>4813.032209663545</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.53</v>
+        <v>-7.38</v>
       </c>
       <c r="L54" t="n">
-        <v>2.55</v>
+        <v>8.27</v>
       </c>
       <c r="M54" t="n">
-        <v>2.24</v>
+        <v>6.84</v>
       </c>
       <c r="N54" t="n">
-        <v>3.12</v>
+        <v>6.15</v>
       </c>
       <c r="O54" t="n">
         <v>5.5</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.94</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>4157</v>
+        <v>4265.9</v>
       </c>
       <c r="I55" t="n">
         <v>4260.820205156679</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
-        <v>8.51</v>
+        <v>6.11</v>
       </c>
       <c r="L55" t="n">
         <v>2.67</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>8.6</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46140.55208333334</v>
+        <v>46141.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>4465.3</v>
+        <v>4420</v>
       </c>
       <c r="I56" t="n">
         <v>4422.426984524557</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>4.67</v>
+        <v>3.61</v>
       </c>
       <c r="L56" t="n">
         <v>7.86</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>6.24</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46148.38541666666</v>
+        <v>46148.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>4345.1</v>
+        <v>4524.1</v>
       </c>
       <c r="I57" t="n">
         <v>4487.147615707583</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>1.69</v>
+        <v>-2.36</v>
       </c>
       <c r="L57" t="n">
-        <v>1.98</v>
+        <v>3.29</v>
       </c>
       <c r="M57" t="n">
         <v>1.63</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>8.23</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>4309</v>
+        <v>4249</v>
       </c>
       <c r="I58" t="n">
         <v>4266.173856410746</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.75</v>
+        <v>-6.08</v>
       </c>
       <c r="L58" t="n">
-        <v>5.47</v>
+        <v>6.16</v>
       </c>
       <c r="M58" t="n">
         <v>2.03</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>7.26</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>4432</v>
+        <v>4512.7</v>
       </c>
       <c r="I59" t="n">
         <v>4441.880100488482</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.31</v>
+        <v>-6.21</v>
       </c>
       <c r="L59" t="n">
-        <v>4.97</v>
+        <v>6.8</v>
       </c>
       <c r="M59" t="n">
-        <v>0.72</v>
+        <v>2.08</v>
       </c>
       <c r="N59" t="n">
         <v>2.94</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>5.6</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>5298</v>
+        <v>5115</v>
       </c>
       <c r="I60" t="n">
         <v>5201.913241130056</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>17.4</v>
+        <v>13.35</v>
       </c>
       <c r="L60" t="n">
         <v>3.61</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>6.94</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46227.55208333334</v>
+        <v>46230.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>5000</v>
+        <v>5222.5</v>
       </c>
       <c r="I61" t="n">
         <v>5217.036111302923</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>2.25</v>
+        <v>-2.1</v>
       </c>
       <c r="L61" t="n">
         <v>4.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.22</v>
       </c>
       <c r="N61" t="n">
-        <v>2.26</v>
+        <v>4.8</v>
       </c>
       <c r="O61" t="n">
         <v>-5.24</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>7.2</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46254.38541666666</v>
+        <v>46254.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>5180.5</v>
+        <v>5160</v>
       </c>
       <c r="I62" t="n">
         <v>5160.683115155254</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="L62" t="n">
         <v>2.44</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>3.56</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>4845</v>
+        <v>4950</v>
       </c>
       <c r="I63" t="n">
         <v>4944.402928261367</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>6.1</v>
+        <v>4.07</v>
       </c>
       <c r="L63" t="n">
         <v>2.33</v>
       </c>
       <c r="M63" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="N63" t="n">
         <v>2.21</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.04</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46303.38541666666</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>4837</v>
+        <v>4790</v>
       </c>
       <c r="I64" t="n">
         <v>4822.079093291404</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.28</v>
+        <v>-3.23</v>
       </c>
       <c r="L64" t="n">
-        <v>2.94</v>
+        <v>3.39</v>
       </c>
       <c r="M64" t="n">
         <v>1</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,12 @@
       <c r="Q65" t="n">
         <v>25</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7036,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.3</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7046,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7056,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7066,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7076,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7086,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="11">
@@ -6341,7 +7126,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.26</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7136,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.79</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7146,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.68</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7156,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.13</v>
+        <v>22.78</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7166,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.6</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7176,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7186,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.32</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="21">
@@ -6421,7 +7206,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -6441,7 +7226,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="25">
@@ -6461,7 +7246,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -6481,7 +7266,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
